--- a/anti-amyloid-npi-analysis/data_local/donanemab_D1-D30_NPI.xlsx
+++ b/anti-amyloid-npi-analysis/data_local/donanemab_D1-D30_NPI.xlsx
@@ -652,11 +652,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="0"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -716,8 +718,71 @@
       <color rgb="FFFFFFFF"/>
       <name val="Yu Gothic"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2937"/>
+      <name val="Yu Gothic"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Yu Gothic"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F2937"/>
+      <name val="Yu Gothic"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -800,8 +865,105 @@
         <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F766E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F766E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -810,14 +972,20 @@
       <diagonal/>
     </border>
     <border/>
+    <border/>
+    <border/>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1"/>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="2"/>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="2"/>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="3"/>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -919,12 +1087,209 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="2" xfId="4"/>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="2" xfId="5" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="2" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="2" xfId="5" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="2" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="2" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="2" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="2" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="2" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="2" xfId="4" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="3" xfId="6"/>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="3" xfId="7" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="3" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="3" xfId="7" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="3" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="3" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="32" borderId="3" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="31" borderId="3" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="3" xfId="6" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="3" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="26" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="26" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="26" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="35" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="35" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="35" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="3" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="37" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="37" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="36" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="36" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="22" fillId="37" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="37" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="22" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="18" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="36" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="22" fillId="37" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="32">
     <dxf>
       <fill>
         <patternFill>
@@ -1051,6 +1416,132 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C3C10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF805600"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C3C10"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF805600"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1143,21 +1634,24 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="NPI_Presence" displayName="NPI_Presence" ref="A1:L37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:L37"/>
-  <x:tableColumns count="12">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="NPI_Presence" displayName="NPI_Presence" ref="A1:O37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:O37"/>
+  <x:tableColumns count="15">
     <x:tableColumn id="1" name="研究番号"/>
     <x:tableColumn id="2" name="時点（原票）"/>
     <x:tableColumn id="3" name="評価日"/>
     <x:tableColumn id="4" name="無関心・アパシー&#10;有無（NPI項目7）"/>
     <x:tableColumn id="5" name="易怒性&#10;有無（NPI項目9）"/>
-    <x:tableColumn id="6" name="無関心・アパシー&#10;1＝あり／0＝なし"/>
-    <x:tableColumn id="7" name="易怒性&#10;1＝あり／0＝なし"/>
-    <x:tableColumn id="8" name="評価日（原票記載）"/>
-    <x:tableColumn id="9" name="原票注記"/>
-    <x:tableColumn id="10" name="情報源PDF"/>
-    <x:tableColumn id="11" name="PDFページ"/>
-    <x:tableColumn id="12" name="確認事項"/>
+    <x:tableColumn id="6" name="アパシー頻度 F&#10;（原票・1～4）"/>
+    <x:tableColumn id="7" name="アパシー重症度 S&#10;（原票・1～3）"/>
+    <x:tableColumn id="8" name="NPI-Apathy score&#10;頻度 × 重症度（0～12）"/>
+    <x:tableColumn id="9" name="無関心・アパシー&#10;1＝あり／0＝なし"/>
+    <x:tableColumn id="10" name="易怒性&#10;1＝あり／0＝なし"/>
+    <x:tableColumn id="11" name="評価日（原票記載）"/>
+    <x:tableColumn id="12" name="原票注記"/>
+    <x:tableColumn id="13" name="情報源PDF"/>
+    <x:tableColumn id="14" name="PDFページ"/>
+    <x:tableColumn id="15" name="確認事項"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1335,25 +1829,25 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26.100000381469727" customHeight="1">
-      <x:c r="A1" s="12" t="inlineStr">
+      <x:c r="A1" s="53" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ドナネマブ研究 D1-30 分割構造マスター</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1" s="12"/>
+      <x:c r="B1" s="53"/>
     </x:row>
     <x:row r="2" ht="48" customHeight="1">
-      <x:c r="A2" s="39" t="inlineStr">
+      <x:c r="A2" s="80" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">作成方針</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2" s="40" t="str">
+      <x:c r="B2" s="81" t="str">
         <x:v>1つのExcelファイル内で MMSE / CDR / MoCA-J / NPI を別シート化。NPIは原票1枚につき1行。原票のない研究番号も明示。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15">
-      <x:c r="A3" s="11" t="inlineStr">
+      <x:c r="A3" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MMSE</x:t>
         </x:is>
@@ -1365,7 +1859,7 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="15">
-      <x:c r="A4" s="11" t="inlineStr">
+      <x:c r="A4" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CDR</x:t>
         </x:is>
@@ -1377,7 +1871,7 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="15">
-      <x:c r="A5" s="11" t="inlineStr">
+      <x:c r="A5" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">MoCA-J</x:t>
         </x:is>
@@ -1389,15 +1883,15 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
-      <x:c r="A6" s="39" t="str">
+      <x:c r="A6" s="80" t="str">
         <x:v>NPI</x:v>
       </x:c>
-      <x:c r="B6" s="40" t="str">
+      <x:c r="B6" s="81" t="str">
         <x:v>旧「精神症状」シートを削除し、NPI原票の項目7「無関心・アパシー」と項目9「易怒性」の有無に置換。丸印を直接転記。従来の問診値からは補完しない。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15">
-      <x:c r="A7" s="11" t="inlineStr">
+      <x:c r="A7" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">統合解析用</x:t>
         </x:is>
@@ -1409,7 +1903,7 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="15">
-      <x:c r="A8" s="11" t="inlineStr">
+      <x:c r="A8" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">要再確認ログ</x:t>
         </x:is>
@@ -1421,7 +1915,7 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="15">
-      <x:c r="A9" s="11" t="inlineStr">
+      <x:c r="A9" s="52" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">注意</x:t>
         </x:is>
@@ -1433,51 +1927,83 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
-      <x:c r="A11" s="36" t="str">
+      <x:c r="A11" s="77" t="str">
         <x:v>NPIの対象原票</x:v>
       </x:c>
-      <x:c r="B11" s="30" t="str">
+      <x:c r="B11" s="71" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf（全14ページ）。8症例・14回の評価。D1、D2、D18～D23の記録を収載。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
-      <x:c r="A12" s="36" t="str">
+      <x:c r="A12" s="77" t="str">
         <x:v>有無と解析用コード</x:v>
       </x:c>
-      <x:c r="B12" s="30" t="str">
+      <x:c r="B12" s="71" t="str">
         <x:v>「あり」＝1、「なし」＝0。解析用コードは有無欄から自動計算。「原票なし」「判定不能」は数値欄を空欄とし、0で補完しない。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
-      <x:c r="A13" s="36" t="str">
+      <x:c r="A13" s="77" t="str">
         <x:v>時点・評価日</x:v>
       </x:c>
-      <x:c r="B13" s="30" t="str">
+      <x:c r="B13" s="71" t="str">
         <x:v>時点は原票どおり。「初回」は治療開始時（0か月）を意味するとは限らない。時点の記載がない場合は推測せず「記載なし」。年月のみの日付は原票記載欄に残す。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
-      <x:c r="A14" s="36" t="str">
+      <x:c r="A14" s="77" t="str">
         <x:v>推定の注記</x:v>
       </x:c>
-      <x:c r="B14" s="30" t="str">
+      <x:c r="B14" s="71" t="str">
         <x:v>p.6・p.10に「推」、p.12・p.13に「推定」の注記あり。有無は原票どおり転記し、推定の対象・方法の確認が必要な記録として区別。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
-      <x:c r="A15" s="36" t="str">
+      <x:c r="A15" s="77" t="str">
         <x:v>欠測の扱い</x:v>
       </x:c>
-      <x:c r="B15" s="30" t="str">
+      <x:c r="B15" s="71" t="str">
         <x:v>添付PDFに該当原票がない22症例は「原票なし」と表示。未実施や症状なしとは判定していない。原票のない評価時点を新たに作成していない。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
-      <x:c r="A16" s="36" t="str">
+      <x:c r="A16" s="77" t="str">
         <x:v>照合方法</x:v>
       </x:c>
-      <x:c r="B16" s="30" t="str">
+      <x:c r="B16" s="71" t="str">
         <x:v>PDFページ欄は添付PDFの先頭から数えたページ番号。研究番号は原票上の手書き番号を使用。氏名・患者IDは転記していない。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="65" customHeight="1">
+      <x:c r="A18" s="117" t="str">
+        <x:v>NPI-Apathy score</x:v>
+      </x:c>
+      <x:c r="B18" s="111" t="str">
+        <x:v>NPI項目7の頻度F×重症度Sで計算（0～12点）。頻度・重症度は原票の記載値を転記。p.2のD1：2×1＝2点、p.1のD2：1×1＝1点。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="65" customHeight="1">
+      <x:c r="A19" s="117" t="str">
+        <x:v>0点と欠測</x:v>
+      </x:c>
+      <x:c r="B19" s="111" t="str">
+        <x:v>原票で「なし」に丸印がある12回分は0点。頻度・重症度の原票空欄は保持。「原票なし」22症例や、症状ありでも頻度・重症度が不足する場合はスコアを空欄とする。原票の推定注記も保持。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="80" customHeight="1">
+      <x:c r="A21" s="117" t="str">
+        <x:v>アパシー消失時の入力ルール</x:v>
+      </x:c>
+      <x:c r="B21" s="111" t="str">
+        <x:v>同一症例で0か月のNPI-Apathy scoreが1以上、かつ18か月のアパシーが「なし」の場合、18か月の頻度＝0、重症度＝0、NPI-Apathy score＝0とする。原票の頻度・重症度が空欄でも、この条件下では研究用の入力値を0とする。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="80" customHeight="1">
+      <x:c r="A22" s="117" t="str">
+        <x:v>今回の適用確認</x:v>
+      </x:c>
+      <x:c r="B22" s="111" t="str">
+        <x:v>現時点のドナネマブNPIシートに18か月の記録はなく、該当行は0件。数値の変更なし。初回・6か月を18か月へ読み替えない。原票なしは欠測のまま保持する。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -15506,1233 +16032,1442 @@
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="23" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="27" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="23" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="49" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="76" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="23" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="23" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="31" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="27" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="25" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="23" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="49" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="76" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="48" customHeight="1">
-      <x:c r="A1" s="25" t="str">
+    <x:row r="1" ht="52" customHeight="1">
+      <x:c r="A1" s="95" t="str">
         <x:v>研究番号</x:v>
       </x:c>
-      <x:c r="B1" s="25" t="str">
+      <x:c r="B1" s="95" t="str">
         <x:v>時点（原票）</x:v>
       </x:c>
-      <x:c r="C1" s="25" t="str">
+      <x:c r="C1" s="95" t="str">
         <x:v>評価日</x:v>
       </x:c>
-      <x:c r="D1" s="25" t="str">
+      <x:c r="D1" s="95" t="str">
         <x:v>無関心・アパシー
 有無（NPI項目7）</x:v>
       </x:c>
-      <x:c r="E1" s="25" t="str">
+      <x:c r="E1" s="95" t="str">
         <x:v>易怒性
 有無（NPI項目9）</x:v>
       </x:c>
-      <x:c r="F1" s="25" t="str">
+      <x:c r="F1" s="95" t="str">
+        <x:v>アパシー頻度 F
+（原票・1～4）</x:v>
+      </x:c>
+      <x:c r="G1" s="95" t="str">
+        <x:v>アパシー重症度 S
+（原票・1～3）</x:v>
+      </x:c>
+      <x:c r="H1" s="95" t="str">
+        <x:v>NPI-Apathy score
+頻度 × 重症度（0～12）</x:v>
+      </x:c>
+      <x:c r="I1" s="95" t="str">
         <x:v>無関心・アパシー
 1＝あり／0＝なし</x:v>
       </x:c>
-      <x:c r="G1" s="25" t="str">
+      <x:c r="J1" s="95" t="str">
         <x:v>易怒性
 1＝あり／0＝なし</x:v>
       </x:c>
-      <x:c r="H1" s="25" t="str">
+      <x:c r="K1" s="95" t="str">
         <x:v>評価日（原票記載）</x:v>
       </x:c>
-      <x:c r="I1" s="25" t="str">
+      <x:c r="L1" s="95" t="str">
         <x:v>原票注記</x:v>
       </x:c>
-      <x:c r="J1" s="25" t="str">
+      <x:c r="M1" s="95" t="str">
         <x:v>情報源PDF</x:v>
       </x:c>
-      <x:c r="K1" s="25" t="str">
+      <x:c r="N1" s="95" t="str">
         <x:v>PDFページ</x:v>
       </x:c>
-      <x:c r="L1" s="25" t="str">
+      <x:c r="O1" s="95" t="str">
         <x:v>確認事項</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="31" t="str">
+      <x:c r="A2" s="88" t="str">
         <x:v>D1</x:v>
       </x:c>
-      <x:c r="B2" s="31" t="str">
+      <x:c r="B2" s="88" t="str">
         <x:v>初回</x:v>
       </x:c>
-      <x:c r="C2" s="32" t="n">
+      <x:c r="C2" s="116" t="n">
         <x:v>46274</x:v>
       </x:c>
-      <x:c r="D2" s="33" t="str">
+      <x:c r="D2" s="91" t="str">
         <x:v>あり</x:v>
       </x:c>
-      <x:c r="E2" s="33" t="str">
+      <x:c r="E2" s="91" t="str">
         <x:v>あり</x:v>
       </x:c>
-      <x:c r="F2" s="34" t="n">
+      <x:c r="F2" s="98" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G2" s="98" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="99" t="n">
+        <x:f>IF(D2="なし",0,IF(AND(D2="あり",ISNUMBER(F2),ISNUMBER(G2)),F2*G2,""))</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I2" s="98" t="n">
         <x:f>IF(D2="あり",1,IF(D2="なし",0,""))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G2" s="34" t="n">
+      <x:c r="J2" s="98" t="n">
         <x:f>IF(E2="あり",1,IF(E2="なし",0,""))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H2" s="33" t="str">
+      <x:c r="K2" s="91" t="str">
         <x:v>2026.9.9</x:v>
       </x:c>
-      <x:c r="I2" s="33" t="str">
+      <x:c r="L2" s="91" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="J2" s="31" t="str">
+      <x:c r="M2" s="88" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K2" s="35" t="n">
+      <x:c r="N2" s="88" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L2" s="36" t="str">
+      <x:c r="O2" s="117" t="str">
         <x:v>原票の「初回」と治療開始時点との対応は要確認。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="21" t="str">
+      <x:c r="A3" s="89" t="str">
         <x:v>D2</x:v>
       </x:c>
-      <x:c r="B3" s="21" t="str">
+      <x:c r="B3" s="89" t="str">
         <x:v>初回</x:v>
       </x:c>
-      <x:c r="C3" s="26" t="n">
+      <x:c r="C3" s="118" t="n">
         <x:v>46275</x:v>
       </x:c>
-      <x:c r="D3" s="28" t="str">
+      <x:c r="D3" s="92" t="str">
         <x:v>あり</x:v>
       </x:c>
-      <x:c r="E3" s="28" t="str">
+      <x:c r="E3" s="92" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="F3" s="29" t="n">
+      <x:c r="F3" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G3" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H3" s="102" t="n">
+        <x:f>IF(D3="なし",0,IF(AND(D3="あり",ISNUMBER(F3),ISNUMBER(G3)),F3*G3,""))</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I3" s="101" t="n">
         <x:f>IF(D3="あり",1,IF(D3="なし",0,""))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G3" s="29" t="n">
+      <x:c r="J3" s="101" t="n">
         <x:f>IF(E3="あり",1,IF(E3="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H3" s="28" t="str">
+      <x:c r="K3" s="92" t="str">
         <x:v>2026.9.10</x:v>
       </x:c>
-      <x:c r="I3" s="28" t="str">
+      <x:c r="L3" s="92" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="J3" s="21" t="str">
+      <x:c r="M3" s="89" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K3" s="27" t="n">
+      <x:c r="N3" s="89" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L3" s="30" t="str">
+      <x:c r="O3" s="119" t="str">
         <x:v>原票の「初回」と治療開始時点との対応は要確認。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="31" t="str">
+      <x:c r="A4" s="88" t="str">
         <x:v>D3</x:v>
       </x:c>
-      <x:c r="B4" s="31" t="str">
+      <x:c r="B4" s="88" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C4" s="32"/>
-      <x:c r="D4" s="33" t="str">
+      <x:c r="C4" s="116"/>
+      <x:c r="D4" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E4" s="33" t="str">
+      <x:c r="E4" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F4" s="34" t="str">
+      <x:c r="F4" s="98"/>
+      <x:c r="G4" s="98"/>
+      <x:c r="H4" s="99" t="str">
+        <x:f>IF(D4="なし",0,IF(AND(D4="あり",ISNUMBER(F4),ISNUMBER(G4)),F4*G4,""))</x:f>
+      </x:c>
+      <x:c r="I4" s="98" t="str">
         <x:f>IF(D4="あり",1,IF(D4="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G4" s="34" t="str">
+      <x:c r="J4" s="98" t="str">
         <x:f>IF(E4="あり",1,IF(E4="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H4" s="33"/>
-      <x:c r="I4" s="33"/>
-      <x:c r="J4" s="31"/>
-      <x:c r="K4" s="35"/>
-      <x:c r="L4" s="36" t="str">
+      <x:c r="K4" s="91"/>
+      <x:c r="L4" s="91"/>
+      <x:c r="M4" s="88"/>
+      <x:c r="N4" s="88"/>
+      <x:c r="O4" s="117" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="21" t="str">
+      <x:c r="A5" s="89" t="str">
         <x:v>D4</x:v>
       </x:c>
-      <x:c r="B5" s="21" t="str">
+      <x:c r="B5" s="89" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C5" s="26"/>
-      <x:c r="D5" s="28" t="str">
+      <x:c r="C5" s="118"/>
+      <x:c r="D5" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E5" s="28" t="str">
+      <x:c r="E5" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F5" s="29" t="str">
+      <x:c r="F5" s="101"/>
+      <x:c r="G5" s="101"/>
+      <x:c r="H5" s="102" t="str">
+        <x:f>IF(D5="なし",0,IF(AND(D5="あり",ISNUMBER(F5),ISNUMBER(G5)),F5*G5,""))</x:f>
+      </x:c>
+      <x:c r="I5" s="101" t="str">
         <x:f>IF(D5="あり",1,IF(D5="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G5" s="29" t="str">
+      <x:c r="J5" s="101" t="str">
         <x:f>IF(E5="あり",1,IF(E5="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H5" s="28"/>
-      <x:c r="I5" s="28"/>
-      <x:c r="J5" s="21"/>
-      <x:c r="K5" s="27"/>
-      <x:c r="L5" s="30" t="str">
+      <x:c r="K5" s="92"/>
+      <x:c r="L5" s="92"/>
+      <x:c r="M5" s="89"/>
+      <x:c r="N5" s="89"/>
+      <x:c r="O5" s="119" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="31" t="str">
+      <x:c r="A6" s="88" t="str">
         <x:v>D5</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="88" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C6" s="32"/>
-      <x:c r="D6" s="33" t="str">
+      <x:c r="C6" s="116"/>
+      <x:c r="D6" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E6" s="33" t="str">
+      <x:c r="E6" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F6" s="34" t="str">
+      <x:c r="F6" s="98"/>
+      <x:c r="G6" s="98"/>
+      <x:c r="H6" s="99" t="str">
+        <x:f>IF(D6="なし",0,IF(AND(D6="あり",ISNUMBER(F6),ISNUMBER(G6)),F6*G6,""))</x:f>
+      </x:c>
+      <x:c r="I6" s="98" t="str">
         <x:f>IF(D6="あり",1,IF(D6="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G6" s="34" t="str">
+      <x:c r="J6" s="98" t="str">
         <x:f>IF(E6="あり",1,IF(E6="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H6" s="33"/>
-      <x:c r="I6" s="33"/>
-      <x:c r="J6" s="31"/>
-      <x:c r="K6" s="35"/>
-      <x:c r="L6" s="36" t="str">
+      <x:c r="K6" s="91"/>
+      <x:c r="L6" s="91"/>
+      <x:c r="M6" s="88"/>
+      <x:c r="N6" s="88"/>
+      <x:c r="O6" s="117" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="21" t="str">
+      <x:c r="A7" s="89" t="str">
         <x:v>D6</x:v>
       </x:c>
-      <x:c r="B7" s="21" t="str">
+      <x:c r="B7" s="89" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C7" s="26"/>
-      <x:c r="D7" s="28" t="str">
+      <x:c r="C7" s="118"/>
+      <x:c r="D7" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E7" s="28" t="str">
+      <x:c r="E7" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F7" s="29" t="str">
+      <x:c r="F7" s="101"/>
+      <x:c r="G7" s="101"/>
+      <x:c r="H7" s="102" t="str">
+        <x:f>IF(D7="なし",0,IF(AND(D7="あり",ISNUMBER(F7),ISNUMBER(G7)),F7*G7,""))</x:f>
+      </x:c>
+      <x:c r="I7" s="101" t="str">
         <x:f>IF(D7="あり",1,IF(D7="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G7" s="29" t="str">
+      <x:c r="J7" s="101" t="str">
         <x:f>IF(E7="あり",1,IF(E7="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H7" s="28"/>
-      <x:c r="I7" s="28"/>
-      <x:c r="J7" s="21"/>
-      <x:c r="K7" s="27"/>
-      <x:c r="L7" s="30" t="str">
+      <x:c r="K7" s="92"/>
+      <x:c r="L7" s="92"/>
+      <x:c r="M7" s="89"/>
+      <x:c r="N7" s="89"/>
+      <x:c r="O7" s="119" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="31" t="str">
+      <x:c r="A8" s="88" t="str">
         <x:v>D7</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="str">
+      <x:c r="B8" s="88" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C8" s="32"/>
-      <x:c r="D8" s="33" t="str">
+      <x:c r="C8" s="116"/>
+      <x:c r="D8" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E8" s="33" t="str">
+      <x:c r="E8" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F8" s="34" t="str">
+      <x:c r="F8" s="98"/>
+      <x:c r="G8" s="98"/>
+      <x:c r="H8" s="99" t="str">
+        <x:f>IF(D8="なし",0,IF(AND(D8="あり",ISNUMBER(F8),ISNUMBER(G8)),F8*G8,""))</x:f>
+      </x:c>
+      <x:c r="I8" s="98" t="str">
         <x:f>IF(D8="あり",1,IF(D8="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G8" s="34" t="str">
+      <x:c r="J8" s="98" t="str">
         <x:f>IF(E8="あり",1,IF(E8="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H8" s="33"/>
-      <x:c r="I8" s="33"/>
-      <x:c r="J8" s="31"/>
-      <x:c r="K8" s="35"/>
-      <x:c r="L8" s="36" t="str">
+      <x:c r="K8" s="91"/>
+      <x:c r="L8" s="91"/>
+      <x:c r="M8" s="88"/>
+      <x:c r="N8" s="88"/>
+      <x:c r="O8" s="117" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="21" t="str">
+      <x:c r="A9" s="89" t="str">
         <x:v>D8</x:v>
       </x:c>
-      <x:c r="B9" s="21" t="str">
+      <x:c r="B9" s="89" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C9" s="26"/>
-      <x:c r="D9" s="28" t="str">
+      <x:c r="C9" s="118"/>
+      <x:c r="D9" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E9" s="28" t="str">
+      <x:c r="E9" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F9" s="29" t="str">
+      <x:c r="F9" s="101"/>
+      <x:c r="G9" s="101"/>
+      <x:c r="H9" s="102" t="str">
+        <x:f>IF(D9="なし",0,IF(AND(D9="あり",ISNUMBER(F9),ISNUMBER(G9)),F9*G9,""))</x:f>
+      </x:c>
+      <x:c r="I9" s="101" t="str">
         <x:f>IF(D9="あり",1,IF(D9="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G9" s="29" t="str">
+      <x:c r="J9" s="101" t="str">
         <x:f>IF(E9="あり",1,IF(E9="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H9" s="28"/>
-      <x:c r="I9" s="28"/>
-      <x:c r="J9" s="21"/>
-      <x:c r="K9" s="27"/>
-      <x:c r="L9" s="30" t="str">
+      <x:c r="K9" s="92"/>
+      <x:c r="L9" s="92"/>
+      <x:c r="M9" s="89"/>
+      <x:c r="N9" s="89"/>
+      <x:c r="O9" s="119" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="31" t="str">
+      <x:c r="A10" s="88" t="str">
         <x:v>D9</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="str">
+      <x:c r="B10" s="88" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C10" s="32"/>
-      <x:c r="D10" s="33" t="str">
+      <x:c r="C10" s="116"/>
+      <x:c r="D10" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E10" s="33" t="str">
+      <x:c r="E10" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F10" s="34" t="str">
+      <x:c r="F10" s="98"/>
+      <x:c r="G10" s="98"/>
+      <x:c r="H10" s="99" t="str">
+        <x:f>IF(D10="なし",0,IF(AND(D10="あり",ISNUMBER(F10),ISNUMBER(G10)),F10*G10,""))</x:f>
+      </x:c>
+      <x:c r="I10" s="98" t="str">
         <x:f>IF(D10="あり",1,IF(D10="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G10" s="34" t="str">
+      <x:c r="J10" s="98" t="str">
         <x:f>IF(E10="あり",1,IF(E10="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H10" s="33"/>
-      <x:c r="I10" s="33"/>
-      <x:c r="J10" s="31"/>
-      <x:c r="K10" s="35"/>
-      <x:c r="L10" s="36" t="str">
+      <x:c r="K10" s="91"/>
+      <x:c r="L10" s="91"/>
+      <x:c r="M10" s="88"/>
+      <x:c r="N10" s="88"/>
+      <x:c r="O10" s="117" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="21" t="str">
+      <x:c r="A11" s="89" t="str">
         <x:v>D10</x:v>
       </x:c>
-      <x:c r="B11" s="21" t="str">
+      <x:c r="B11" s="89" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C11" s="26"/>
-      <x:c r="D11" s="28" t="str">
+      <x:c r="C11" s="118"/>
+      <x:c r="D11" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E11" s="28" t="str">
+      <x:c r="E11" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F11" s="29" t="str">
+      <x:c r="F11" s="101"/>
+      <x:c r="G11" s="101"/>
+      <x:c r="H11" s="102" t="str">
+        <x:f>IF(D11="なし",0,IF(AND(D11="あり",ISNUMBER(F11),ISNUMBER(G11)),F11*G11,""))</x:f>
+      </x:c>
+      <x:c r="I11" s="101" t="str">
         <x:f>IF(D11="あり",1,IF(D11="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G11" s="29" t="str">
+      <x:c r="J11" s="101" t="str">
         <x:f>IF(E11="あり",1,IF(E11="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H11" s="28"/>
-      <x:c r="I11" s="28"/>
-      <x:c r="J11" s="21"/>
-      <x:c r="K11" s="27"/>
-      <x:c r="L11" s="30" t="str">
+      <x:c r="K11" s="92"/>
+      <x:c r="L11" s="92"/>
+      <x:c r="M11" s="89"/>
+      <x:c r="N11" s="89"/>
+      <x:c r="O11" s="119" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="31" t="str">
+      <x:c r="A12" s="88" t="str">
         <x:v>D11</x:v>
       </x:c>
-      <x:c r="B12" s="31" t="str">
+      <x:c r="B12" s="88" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C12" s="32"/>
-      <x:c r="D12" s="33" t="str">
+      <x:c r="C12" s="116"/>
+      <x:c r="D12" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E12" s="33" t="str">
+      <x:c r="E12" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F12" s="34" t="str">
+      <x:c r="F12" s="98"/>
+      <x:c r="G12" s="98"/>
+      <x:c r="H12" s="99" t="str">
+        <x:f>IF(D12="なし",0,IF(AND(D12="あり",ISNUMBER(F12),ISNUMBER(G12)),F12*G12,""))</x:f>
+      </x:c>
+      <x:c r="I12" s="98" t="str">
         <x:f>IF(D12="あり",1,IF(D12="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G12" s="34" t="str">
+      <x:c r="J12" s="98" t="str">
         <x:f>IF(E12="あり",1,IF(E12="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H12" s="33"/>
-      <x:c r="I12" s="33"/>
-      <x:c r="J12" s="31"/>
-      <x:c r="K12" s="35"/>
-      <x:c r="L12" s="36" t="str">
+      <x:c r="K12" s="91"/>
+      <x:c r="L12" s="91"/>
+      <x:c r="M12" s="88"/>
+      <x:c r="N12" s="88"/>
+      <x:c r="O12" s="117" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="21" t="str">
+      <x:c r="A13" s="89" t="str">
         <x:v>D12</x:v>
       </x:c>
-      <x:c r="B13" s="21" t="str">
+      <x:c r="B13" s="89" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C13" s="26"/>
-      <x:c r="D13" s="28" t="str">
+      <x:c r="C13" s="118"/>
+      <x:c r="D13" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E13" s="28" t="str">
+      <x:c r="E13" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F13" s="29" t="str">
+      <x:c r="F13" s="101"/>
+      <x:c r="G13" s="101"/>
+      <x:c r="H13" s="102" t="str">
+        <x:f>IF(D13="なし",0,IF(AND(D13="あり",ISNUMBER(F13),ISNUMBER(G13)),F13*G13,""))</x:f>
+      </x:c>
+      <x:c r="I13" s="101" t="str">
         <x:f>IF(D13="あり",1,IF(D13="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G13" s="29" t="str">
+      <x:c r="J13" s="101" t="str">
         <x:f>IF(E13="あり",1,IF(E13="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H13" s="28"/>
-      <x:c r="I13" s="28"/>
-      <x:c r="J13" s="21"/>
-      <x:c r="K13" s="27"/>
-      <x:c r="L13" s="30" t="str">
+      <x:c r="K13" s="92"/>
+      <x:c r="L13" s="92"/>
+      <x:c r="M13" s="89"/>
+      <x:c r="N13" s="89"/>
+      <x:c r="O13" s="119" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="31" t="str">
+      <x:c r="A14" s="88" t="str">
         <x:v>D13</x:v>
       </x:c>
-      <x:c r="B14" s="31" t="str">
+      <x:c r="B14" s="88" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C14" s="32"/>
-      <x:c r="D14" s="33" t="str">
+      <x:c r="C14" s="116"/>
+      <x:c r="D14" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E14" s="33" t="str">
+      <x:c r="E14" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F14" s="34" t="str">
+      <x:c r="F14" s="98"/>
+      <x:c r="G14" s="98"/>
+      <x:c r="H14" s="99" t="str">
+        <x:f>IF(D14="なし",0,IF(AND(D14="あり",ISNUMBER(F14),ISNUMBER(G14)),F14*G14,""))</x:f>
+      </x:c>
+      <x:c r="I14" s="98" t="str">
         <x:f>IF(D14="あり",1,IF(D14="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G14" s="34" t="str">
+      <x:c r="J14" s="98" t="str">
         <x:f>IF(E14="あり",1,IF(E14="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H14" s="33"/>
-      <x:c r="I14" s="33"/>
-      <x:c r="J14" s="31"/>
-      <x:c r="K14" s="35"/>
-      <x:c r="L14" s="36" t="str">
+      <x:c r="K14" s="91"/>
+      <x:c r="L14" s="91"/>
+      <x:c r="M14" s="88"/>
+      <x:c r="N14" s="88"/>
+      <x:c r="O14" s="117" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="21" t="str">
+      <x:c r="A15" s="89" t="str">
         <x:v>D14</x:v>
       </x:c>
-      <x:c r="B15" s="21" t="str">
+      <x:c r="B15" s="89" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C15" s="26"/>
-      <x:c r="D15" s="28" t="str">
+      <x:c r="C15" s="118"/>
+      <x:c r="D15" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E15" s="28" t="str">
+      <x:c r="E15" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F15" s="29" t="str">
+      <x:c r="F15" s="101"/>
+      <x:c r="G15" s="101"/>
+      <x:c r="H15" s="102" t="str">
+        <x:f>IF(D15="なし",0,IF(AND(D15="あり",ISNUMBER(F15),ISNUMBER(G15)),F15*G15,""))</x:f>
+      </x:c>
+      <x:c r="I15" s="101" t="str">
         <x:f>IF(D15="あり",1,IF(D15="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G15" s="29" t="str">
+      <x:c r="J15" s="101" t="str">
         <x:f>IF(E15="あり",1,IF(E15="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H15" s="28"/>
-      <x:c r="I15" s="28"/>
-      <x:c r="J15" s="21"/>
-      <x:c r="K15" s="27"/>
-      <x:c r="L15" s="30" t="str">
+      <x:c r="K15" s="92"/>
+      <x:c r="L15" s="92"/>
+      <x:c r="M15" s="89"/>
+      <x:c r="N15" s="89"/>
+      <x:c r="O15" s="119" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="31" t="str">
+      <x:c r="A16" s="88" t="str">
         <x:v>D15</x:v>
       </x:c>
-      <x:c r="B16" s="31" t="str">
+      <x:c r="B16" s="88" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C16" s="32"/>
-      <x:c r="D16" s="33" t="str">
+      <x:c r="C16" s="116"/>
+      <x:c r="D16" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E16" s="33" t="str">
+      <x:c r="E16" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F16" s="34" t="str">
+      <x:c r="F16" s="98"/>
+      <x:c r="G16" s="98"/>
+      <x:c r="H16" s="99" t="str">
+        <x:f>IF(D16="なし",0,IF(AND(D16="あり",ISNUMBER(F16),ISNUMBER(G16)),F16*G16,""))</x:f>
+      </x:c>
+      <x:c r="I16" s="98" t="str">
         <x:f>IF(D16="あり",1,IF(D16="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G16" s="34" t="str">
+      <x:c r="J16" s="98" t="str">
         <x:f>IF(E16="あり",1,IF(E16="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H16" s="33"/>
-      <x:c r="I16" s="33"/>
-      <x:c r="J16" s="31"/>
-      <x:c r="K16" s="35"/>
-      <x:c r="L16" s="36" t="str">
+      <x:c r="K16" s="91"/>
+      <x:c r="L16" s="91"/>
+      <x:c r="M16" s="88"/>
+      <x:c r="N16" s="88"/>
+      <x:c r="O16" s="117" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="21" t="str">
+      <x:c r="A17" s="89" t="str">
         <x:v>D16</x:v>
       </x:c>
-      <x:c r="B17" s="21" t="str">
+      <x:c r="B17" s="89" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C17" s="26"/>
-      <x:c r="D17" s="28" t="str">
+      <x:c r="C17" s="118"/>
+      <x:c r="D17" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E17" s="28" t="str">
+      <x:c r="E17" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F17" s="29" t="str">
+      <x:c r="F17" s="101"/>
+      <x:c r="G17" s="101"/>
+      <x:c r="H17" s="102" t="str">
+        <x:f>IF(D17="なし",0,IF(AND(D17="あり",ISNUMBER(F17),ISNUMBER(G17)),F17*G17,""))</x:f>
+      </x:c>
+      <x:c r="I17" s="101" t="str">
         <x:f>IF(D17="あり",1,IF(D17="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G17" s="29" t="str">
+      <x:c r="J17" s="101" t="str">
         <x:f>IF(E17="あり",1,IF(E17="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H17" s="28"/>
-      <x:c r="I17" s="28"/>
-      <x:c r="J17" s="21"/>
-      <x:c r="K17" s="27"/>
-      <x:c r="L17" s="30" t="str">
+      <x:c r="K17" s="92"/>
+      <x:c r="L17" s="92"/>
+      <x:c r="M17" s="89"/>
+      <x:c r="N17" s="89"/>
+      <x:c r="O17" s="119" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
-      <x:c r="A18" s="31" t="str">
+      <x:c r="A18" s="88" t="str">
         <x:v>D17</x:v>
       </x:c>
-      <x:c r="B18" s="31" t="str">
+      <x:c r="B18" s="88" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C18" s="32"/>
-      <x:c r="D18" s="33" t="str">
+      <x:c r="C18" s="116"/>
+      <x:c r="D18" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E18" s="33" t="str">
+      <x:c r="E18" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F18" s="34" t="str">
+      <x:c r="F18" s="98"/>
+      <x:c r="G18" s="98"/>
+      <x:c r="H18" s="99" t="str">
+        <x:f>IF(D18="なし",0,IF(AND(D18="あり",ISNUMBER(F18),ISNUMBER(G18)),F18*G18,""))</x:f>
+      </x:c>
+      <x:c r="I18" s="98" t="str">
         <x:f>IF(D18="あり",1,IF(D18="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G18" s="34" t="str">
+      <x:c r="J18" s="98" t="str">
         <x:f>IF(E18="あり",1,IF(E18="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H18" s="33"/>
-      <x:c r="I18" s="33"/>
-      <x:c r="J18" s="31"/>
-      <x:c r="K18" s="35"/>
-      <x:c r="L18" s="36" t="str">
+      <x:c r="K18" s="91"/>
+      <x:c r="L18" s="91"/>
+      <x:c r="M18" s="88"/>
+      <x:c r="N18" s="88"/>
+      <x:c r="O18" s="117" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
-      <x:c r="A19" s="21" t="str">
+      <x:c r="A19" s="89" t="str">
         <x:v>D18</x:v>
       </x:c>
-      <x:c r="B19" s="21" t="str">
+      <x:c r="B19" s="89" t="str">
         <x:v>初回</x:v>
       </x:c>
-      <x:c r="C19" s="26" t="n">
+      <x:c r="C19" s="118" t="n">
         <x:v>46029</x:v>
       </x:c>
-      <x:c r="D19" s="28" t="str">
+      <x:c r="D19" s="92" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="E19" s="28" t="str">
+      <x:c r="E19" s="92" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="F19" s="29" t="n">
+      <x:c r="F19" s="101"/>
+      <x:c r="G19" s="101"/>
+      <x:c r="H19" s="102" t="n">
+        <x:f>IF(D19="なし",0,IF(AND(D19="あり",ISNUMBER(F19),ISNUMBER(G19)),F19*G19,""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="101" t="n">
         <x:f>IF(D19="あり",1,IF(D19="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="29" t="n">
+      <x:c r="J19" s="101" t="n">
         <x:f>IF(E19="あり",1,IF(E19="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="28" t="str">
+      <x:c r="K19" s="92" t="str">
         <x:v>2026.1.7</x:v>
       </x:c>
-      <x:c r="I19" s="28" t="str">
+      <x:c r="L19" s="92" t="str">
         <x:v>推定</x:v>
       </x:c>
-      <x:c r="J19" s="21" t="str">
+      <x:c r="M19" s="89" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K19" s="27" t="n">
+      <x:c r="N19" s="89" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="L19" s="30" t="str">
+      <x:c r="O19" s="119" t="str">
         <x:v>原票に「推定」の注記あり。推定の対象・方法は要確認。</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="21" t="str">
+      <x:c r="A20" s="89" t="str">
         <x:v>D18</x:v>
       </x:c>
-      <x:c r="B20" s="21" t="str">
+      <x:c r="B20" s="89" t="str">
         <x:v>6か月</x:v>
       </x:c>
-      <x:c r="C20" s="26" t="n">
+      <x:c r="C20" s="118" t="n">
         <x:v>46239</x:v>
       </x:c>
-      <x:c r="D20" s="28" t="str">
+      <x:c r="D20" s="92" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="E20" s="28" t="str">
+      <x:c r="E20" s="92" t="str">
         <x:v>あり</x:v>
       </x:c>
-      <x:c r="F20" s="29" t="n">
+      <x:c r="F20" s="101"/>
+      <x:c r="G20" s="101"/>
+      <x:c r="H20" s="102" t="n">
+        <x:f>IF(D20="なし",0,IF(AND(D20="あり",ISNUMBER(F20),ISNUMBER(G20)),F20*G20,""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I20" s="101" t="n">
         <x:f>IF(D20="あり",1,IF(D20="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="29" t="n">
+      <x:c r="J20" s="101" t="n">
         <x:f>IF(E20="あり",1,IF(E20="なし",0,""))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H20" s="28" t="str">
+      <x:c r="K20" s="92" t="str">
         <x:v>2026.8.5</x:v>
       </x:c>
-      <x:c r="I20" s="28" t="str">
+      <x:c r="L20" s="92" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="J20" s="21" t="str">
+      <x:c r="M20" s="89" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K20" s="27" t="n">
+      <x:c r="N20" s="89" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L20" s="30"/>
+      <x:c r="O20" s="119"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
-      <x:c r="A21" s="31" t="str">
+      <x:c r="A21" s="88" t="str">
         <x:v>D19</x:v>
       </x:c>
-      <x:c r="B21" s="31" t="str">
+      <x:c r="B21" s="88" t="str">
         <x:v>初回</x:v>
       </x:c>
-      <x:c r="C21" s="32" t="n">
+      <x:c r="C21" s="116" t="n">
         <x:v>46044</x:v>
       </x:c>
-      <x:c r="D21" s="33" t="str">
+      <x:c r="D21" s="91" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="E21" s="33" t="str">
+      <x:c r="E21" s="91" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="F21" s="34" t="n">
+      <x:c r="F21" s="98"/>
+      <x:c r="G21" s="98"/>
+      <x:c r="H21" s="99" t="n">
+        <x:f>IF(D21="なし",0,IF(AND(D21="あり",ISNUMBER(F21),ISNUMBER(G21)),F21*G21,""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I21" s="98" t="n">
         <x:f>IF(D21="あり",1,IF(D21="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="34" t="n">
+      <x:c r="J21" s="98" t="n">
         <x:f>IF(E21="あり",1,IF(E21="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="33" t="str">
+      <x:c r="K21" s="91" t="str">
         <x:v>2026.1.22</x:v>
       </x:c>
-      <x:c r="I21" s="33" t="str">
+      <x:c r="L21" s="91" t="str">
         <x:v>推定</x:v>
       </x:c>
-      <x:c r="J21" s="31" t="str">
+      <x:c r="M21" s="88" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K21" s="35" t="n">
+      <x:c r="N21" s="88" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="L21" s="36" t="str">
+      <x:c r="O21" s="117" t="str">
         <x:v>原票に「推定」の注記あり。推定の対象・方法は要確認。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
-      <x:c r="A22" s="31" t="str">
+      <x:c r="A22" s="88" t="str">
         <x:v>D19</x:v>
       </x:c>
-      <x:c r="B22" s="31" t="str">
+      <x:c r="B22" s="88" t="str">
         <x:v>6か月フォロー</x:v>
       </x:c>
-      <x:c r="C22" s="32" t="n">
+      <x:c r="C22" s="116" t="n">
         <x:v>46247</x:v>
       </x:c>
-      <x:c r="D22" s="33" t="str">
+      <x:c r="D22" s="91" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="E22" s="33" t="str">
+      <x:c r="E22" s="91" t="str">
         <x:v>あり</x:v>
       </x:c>
-      <x:c r="F22" s="34" t="n">
+      <x:c r="F22" s="98"/>
+      <x:c r="G22" s="98"/>
+      <x:c r="H22" s="99" t="n">
+        <x:f>IF(D22="なし",0,IF(AND(D22="あり",ISNUMBER(F22),ISNUMBER(G22)),F22*G22,""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="98" t="n">
         <x:f>IF(D22="あり",1,IF(D22="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="34" t="n">
+      <x:c r="J22" s="98" t="n">
         <x:f>IF(E22="あり",1,IF(E22="なし",0,""))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H22" s="33" t="str">
+      <x:c r="K22" s="91" t="str">
         <x:v>2026.8.13</x:v>
       </x:c>
-      <x:c r="I22" s="33" t="str">
+      <x:c r="L22" s="91" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="J22" s="31" t="str">
+      <x:c r="M22" s="88" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K22" s="35" t="n">
+      <x:c r="N22" s="88" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L22" s="36"/>
+      <x:c r="O22" s="117"/>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
-      <x:c r="A23" s="21" t="str">
+      <x:c r="A23" s="89" t="str">
         <x:v>D20</x:v>
       </x:c>
-      <x:c r="B23" s="21" t="str">
+      <x:c r="B23" s="89" t="str">
         <x:v>初回</x:v>
       </x:c>
-      <x:c r="C23" s="26" t="n">
+      <x:c r="C23" s="118" t="n">
         <x:v>46028</x:v>
       </x:c>
-      <x:c r="D23" s="28" t="str">
+      <x:c r="D23" s="92" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="E23" s="28" t="str">
+      <x:c r="E23" s="92" t="str">
         <x:v>あり</x:v>
       </x:c>
-      <x:c r="F23" s="29" t="n">
+      <x:c r="F23" s="101"/>
+      <x:c r="G23" s="101"/>
+      <x:c r="H23" s="102" t="n">
+        <x:f>IF(D23="なし",0,IF(AND(D23="あり",ISNUMBER(F23),ISNUMBER(G23)),F23*G23,""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I23" s="101" t="n">
         <x:f>IF(D23="あり",1,IF(D23="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="29" t="n">
+      <x:c r="J23" s="101" t="n">
         <x:f>IF(E23="あり",1,IF(E23="なし",0,""))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H23" s="28" t="str">
+      <x:c r="K23" s="92" t="str">
         <x:v>2026.1.6</x:v>
       </x:c>
-      <x:c r="I23" s="28" t="str">
+      <x:c r="L23" s="92" t="str">
         <x:v>推</x:v>
       </x:c>
-      <x:c r="J23" s="21" t="str">
+      <x:c r="M23" s="89" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K23" s="27" t="n">
+      <x:c r="N23" s="89" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L23" s="30" t="str">
+      <x:c r="O23" s="119" t="str">
         <x:v>原票に「推」の注記あり。推定の対象・方法は要確認。</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
-      <x:c r="A24" s="21" t="str">
+      <x:c r="A24" s="89" t="str">
         <x:v>D20</x:v>
       </x:c>
-      <x:c r="B24" s="21" t="str">
+      <x:c r="B24" s="89" t="str">
         <x:v>6か月フォロー</x:v>
       </x:c>
-      <x:c r="C24" s="26" t="n">
+      <x:c r="C24" s="118" t="n">
         <x:v>46248</x:v>
       </x:c>
-      <x:c r="D24" s="28" t="str">
+      <x:c r="D24" s="92" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="E24" s="28" t="str">
+      <x:c r="E24" s="92" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="F24" s="29" t="n">
+      <x:c r="F24" s="101"/>
+      <x:c r="G24" s="101"/>
+      <x:c r="H24" s="102" t="n">
+        <x:f>IF(D24="なし",0,IF(AND(D24="あり",ISNUMBER(F24),ISNUMBER(G24)),F24*G24,""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I24" s="101" t="n">
         <x:f>IF(D24="あり",1,IF(D24="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="29" t="n">
+      <x:c r="J24" s="101" t="n">
         <x:f>IF(E24="あり",1,IF(E24="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H24" s="28" t="str">
+      <x:c r="K24" s="92" t="str">
         <x:v>2026.8.14</x:v>
       </x:c>
-      <x:c r="I24" s="28" t="str">
+      <x:c r="L24" s="92" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="J24" s="21" t="str">
+      <x:c r="M24" s="89" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K24" s="27" t="n">
+      <x:c r="N24" s="89" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="L24" s="30"/>
+      <x:c r="O24" s="119"/>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
-      <x:c r="A25" s="31" t="str">
+      <x:c r="A25" s="88" t="str">
         <x:v>D21</x:v>
       </x:c>
-      <x:c r="B25" s="31" t="str">
+      <x:c r="B25" s="88" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="C25" s="32"/>
-      <x:c r="D25" s="33" t="str">
+      <x:c r="C25" s="116"/>
+      <x:c r="D25" s="91" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="E25" s="33" t="str">
+      <x:c r="E25" s="91" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="F25" s="34" t="n">
+      <x:c r="F25" s="98"/>
+      <x:c r="G25" s="98"/>
+      <x:c r="H25" s="99" t="n">
+        <x:f>IF(D25="なし",0,IF(AND(D25="あり",ISNUMBER(F25),ISNUMBER(G25)),F25*G25,""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" s="98" t="n">
         <x:f>IF(D25="あり",1,IF(D25="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="34" t="n">
+      <x:c r="J25" s="98" t="n">
         <x:f>IF(E25="あり",1,IF(E25="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H25" s="33" t="str">
+      <x:c r="K25" s="91" t="str">
         <x:v>2026.1</x:v>
       </x:c>
-      <x:c r="I25" s="33" t="str">
+      <x:c r="L25" s="91" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="J25" s="31" t="str">
+      <x:c r="M25" s="88" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K25" s="35" t="n">
+      <x:c r="N25" s="88" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="L25" s="36" t="str">
+      <x:c r="O25" s="117" t="str">
         <x:v>日付は年月のみ。時点の記載なし。</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
-      <x:c r="A26" s="31" t="str">
+      <x:c r="A26" s="88" t="str">
         <x:v>D21</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="88" t="str">
         <x:v>6か月フォロー</x:v>
       </x:c>
-      <x:c r="C26" s="32" t="n">
+      <x:c r="C26" s="116" t="n">
         <x:v>46267</x:v>
       </x:c>
-      <x:c r="D26" s="33" t="str">
+      <x:c r="D26" s="91" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="E26" s="33" t="str">
+      <x:c r="E26" s="91" t="str">
         <x:v>あり</x:v>
       </x:c>
-      <x:c r="F26" s="34" t="n">
+      <x:c r="F26" s="98"/>
+      <x:c r="G26" s="98"/>
+      <x:c r="H26" s="99" t="n">
+        <x:f>IF(D26="なし",0,IF(AND(D26="あり",ISNUMBER(F26),ISNUMBER(G26)),F26*G26,""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" s="98" t="n">
         <x:f>IF(D26="あり",1,IF(D26="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="34" t="n">
+      <x:c r="J26" s="98" t="n">
         <x:f>IF(E26="あり",1,IF(E26="なし",0,""))</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H26" s="33" t="str">
+      <x:c r="K26" s="91" t="str">
         <x:v>2026.9.2</x:v>
       </x:c>
-      <x:c r="I26" s="33" t="str">
+      <x:c r="L26" s="91" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="J26" s="31" t="str">
+      <x:c r="M26" s="88" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K26" s="35" t="n">
+      <x:c r="N26" s="88" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="L26" s="36"/>
+      <x:c r="O26" s="117"/>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
-      <x:c r="A27" s="21" t="str">
+      <x:c r="A27" s="89" t="str">
         <x:v>D22</x:v>
       </x:c>
-      <x:c r="B27" s="21" t="str">
+      <x:c r="B27" s="89" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="C27" s="26"/>
-      <x:c r="D27" s="28" t="str">
+      <x:c r="C27" s="118"/>
+      <x:c r="D27" s="92" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="E27" s="28" t="str">
+      <x:c r="E27" s="92" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="F27" s="29" t="n">
+      <x:c r="F27" s="101"/>
+      <x:c r="G27" s="101"/>
+      <x:c r="H27" s="102" t="n">
+        <x:f>IF(D27="なし",0,IF(AND(D27="あり",ISNUMBER(F27),ISNUMBER(G27)),F27*G27,""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" s="101" t="n">
         <x:f>IF(D27="あり",1,IF(D27="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="29" t="n">
+      <x:c r="J27" s="101" t="n">
         <x:f>IF(E27="あり",1,IF(E27="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="28" t="str">
+      <x:c r="K27" s="92" t="str">
         <x:v>2026.3</x:v>
       </x:c>
-      <x:c r="I27" s="28" t="str">
+      <x:c r="L27" s="92" t="str">
         <x:v>推</x:v>
       </x:c>
-      <x:c r="J27" s="21" t="str">
+      <x:c r="M27" s="89" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K27" s="27" t="n">
+      <x:c r="N27" s="89" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="L27" s="30" t="str">
+      <x:c r="O27" s="119" t="str">
         <x:v>日付は年月のみ。時点の記載なし。 原票に「推」の注記あり。推定の対象・方法は要確認。</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
-      <x:c r="A28" s="21" t="str">
+      <x:c r="A28" s="89" t="str">
         <x:v>D22</x:v>
       </x:c>
-      <x:c r="B28" s="21" t="str">
+      <x:c r="B28" s="89" t="str">
         <x:v>6か月フォロー</x:v>
       </x:c>
-      <x:c r="C28" s="26" t="n">
+      <x:c r="C28" s="118" t="n">
         <x:v>46268</x:v>
       </x:c>
-      <x:c r="D28" s="28" t="str">
+      <x:c r="D28" s="92" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="E28" s="28" t="str">
+      <x:c r="E28" s="92" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="F28" s="29" t="n">
+      <x:c r="F28" s="101"/>
+      <x:c r="G28" s="101"/>
+      <x:c r="H28" s="102" t="n">
+        <x:f>IF(D28="なし",0,IF(AND(D28="あり",ISNUMBER(F28),ISNUMBER(G28)),F28*G28,""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" s="101" t="n">
         <x:f>IF(D28="あり",1,IF(D28="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="29" t="n">
+      <x:c r="J28" s="101" t="n">
         <x:f>IF(E28="あり",1,IF(E28="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="28" t="str">
+      <x:c r="K28" s="92" t="str">
         <x:v>2026.9.3</x:v>
       </x:c>
-      <x:c r="I28" s="28" t="str">
+      <x:c r="L28" s="92" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="J28" s="21" t="str">
+      <x:c r="M28" s="89" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K28" s="27" t="n">
+      <x:c r="N28" s="89" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L28" s="30"/>
+      <x:c r="O28" s="119"/>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
-      <x:c r="A29" s="31" t="str">
+      <x:c r="A29" s="88" t="str">
         <x:v>D23</x:v>
       </x:c>
-      <x:c r="B29" s="31" t="str">
+      <x:c r="B29" s="88" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="C29" s="32"/>
-      <x:c r="D29" s="33" t="str">
+      <x:c r="C29" s="116"/>
+      <x:c r="D29" s="91" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="E29" s="33" t="str">
+      <x:c r="E29" s="91" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="F29" s="34" t="n">
+      <x:c r="F29" s="98"/>
+      <x:c r="G29" s="98"/>
+      <x:c r="H29" s="99" t="n">
+        <x:f>IF(D29="なし",0,IF(AND(D29="あり",ISNUMBER(F29),ISNUMBER(G29)),F29*G29,""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" s="98" t="n">
         <x:f>IF(D29="あり",1,IF(D29="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="34" t="n">
+      <x:c r="J29" s="98" t="n">
         <x:f>IF(E29="あり",1,IF(E29="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="33" t="str">
+      <x:c r="K29" s="91" t="str">
         <x:v>2026.3</x:v>
       </x:c>
-      <x:c r="I29" s="33" t="str">
+      <x:c r="L29" s="91" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="J29" s="31" t="str">
+      <x:c r="M29" s="88" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K29" s="35" t="n">
+      <x:c r="N29" s="88" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="L29" s="36" t="str">
+      <x:c r="O29" s="117" t="str">
         <x:v>日付は年月のみ。時点の記載なし。</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
-      <x:c r="A30" s="31" t="str">
+      <x:c r="A30" s="88" t="str">
         <x:v>D23</x:v>
       </x:c>
-      <x:c r="B30" s="31" t="str">
+      <x:c r="B30" s="88" t="str">
         <x:v>6か月フォロー</x:v>
       </x:c>
-      <x:c r="C30" s="32" t="n">
+      <x:c r="C30" s="116" t="n">
         <x:v>46269</x:v>
       </x:c>
-      <x:c r="D30" s="33" t="str">
+      <x:c r="D30" s="91" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="E30" s="33" t="str">
+      <x:c r="E30" s="91" t="str">
         <x:v>なし</x:v>
       </x:c>
-      <x:c r="F30" s="34" t="n">
+      <x:c r="F30" s="98"/>
+      <x:c r="G30" s="98"/>
+      <x:c r="H30" s="99" t="n">
+        <x:f>IF(D30="なし",0,IF(AND(D30="あり",ISNUMBER(F30),ISNUMBER(G30)),F30*G30,""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" s="98" t="n">
         <x:f>IF(D30="あり",1,IF(D30="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="34" t="n">
+      <x:c r="J30" s="98" t="n">
         <x:f>IF(E30="あり",1,IF(E30="なし",0,""))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="33" t="str">
+      <x:c r="K30" s="91" t="str">
         <x:v>2026.9.4</x:v>
       </x:c>
-      <x:c r="I30" s="33" t="str">
+      <x:c r="L30" s="91" t="str">
         <x:v>記載なし</x:v>
       </x:c>
-      <x:c r="J30" s="31" t="str">
+      <x:c r="M30" s="88" t="str">
         <x:v>ドナネマブのNPI、9.18取り込み(1).pdf</x:v>
       </x:c>
-      <x:c r="K30" s="35" t="n">
+      <x:c r="N30" s="88" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L30" s="36"/>
+      <x:c r="O30" s="117"/>
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
-      <x:c r="A31" s="21" t="str">
+      <x:c r="A31" s="89" t="str">
         <x:v>D24</x:v>
       </x:c>
-      <x:c r="B31" s="21" t="str">
+      <x:c r="B31" s="89" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C31" s="26"/>
-      <x:c r="D31" s="28" t="str">
+      <x:c r="C31" s="118"/>
+      <x:c r="D31" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E31" s="28" t="str">
+      <x:c r="E31" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F31" s="29" t="str">
+      <x:c r="F31" s="101"/>
+      <x:c r="G31" s="101"/>
+      <x:c r="H31" s="102" t="str">
+        <x:f>IF(D31="なし",0,IF(AND(D31="あり",ISNUMBER(F31),ISNUMBER(G31)),F31*G31,""))</x:f>
+      </x:c>
+      <x:c r="I31" s="101" t="str">
         <x:f>IF(D31="あり",1,IF(D31="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G31" s="29" t="str">
+      <x:c r="J31" s="101" t="str">
         <x:f>IF(E31="あり",1,IF(E31="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H31" s="28"/>
-      <x:c r="I31" s="28"/>
-      <x:c r="J31" s="21"/>
-      <x:c r="K31" s="27"/>
-      <x:c r="L31" s="30" t="str">
+      <x:c r="K31" s="92"/>
+      <x:c r="L31" s="92"/>
+      <x:c r="M31" s="89"/>
+      <x:c r="N31" s="89"/>
+      <x:c r="O31" s="119" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="30" customHeight="1">
-      <x:c r="A32" s="31" t="str">
+      <x:c r="A32" s="88" t="str">
         <x:v>D25</x:v>
       </x:c>
-      <x:c r="B32" s="31" t="str">
+      <x:c r="B32" s="88" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C32" s="32"/>
-      <x:c r="D32" s="33" t="str">
+      <x:c r="C32" s="116"/>
+      <x:c r="D32" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E32" s="33" t="str">
+      <x:c r="E32" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F32" s="34" t="str">
+      <x:c r="F32" s="98"/>
+      <x:c r="G32" s="98"/>
+      <x:c r="H32" s="99" t="str">
+        <x:f>IF(D32="なし",0,IF(AND(D32="あり",ISNUMBER(F32),ISNUMBER(G32)),F32*G32,""))</x:f>
+      </x:c>
+      <x:c r="I32" s="98" t="str">
         <x:f>IF(D32="あり",1,IF(D32="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G32" s="34" t="str">
+      <x:c r="J32" s="98" t="str">
         <x:f>IF(E32="あり",1,IF(E32="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H32" s="33"/>
-      <x:c r="I32" s="33"/>
-      <x:c r="J32" s="31"/>
-      <x:c r="K32" s="35"/>
-      <x:c r="L32" s="36" t="str">
+      <x:c r="K32" s="91"/>
+      <x:c r="L32" s="91"/>
+      <x:c r="M32" s="88"/>
+      <x:c r="N32" s="88"/>
+      <x:c r="O32" s="117" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="30" customHeight="1">
-      <x:c r="A33" s="21" t="str">
+      <x:c r="A33" s="89" t="str">
         <x:v>D26</x:v>
       </x:c>
-      <x:c r="B33" s="21" t="str">
+      <x:c r="B33" s="89" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C33" s="26"/>
-      <x:c r="D33" s="28" t="str">
+      <x:c r="C33" s="118"/>
+      <x:c r="D33" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E33" s="28" t="str">
+      <x:c r="E33" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F33" s="29" t="str">
+      <x:c r="F33" s="101"/>
+      <x:c r="G33" s="101"/>
+      <x:c r="H33" s="102" t="str">
+        <x:f>IF(D33="なし",0,IF(AND(D33="あり",ISNUMBER(F33),ISNUMBER(G33)),F33*G33,""))</x:f>
+      </x:c>
+      <x:c r="I33" s="101" t="str">
         <x:f>IF(D33="あり",1,IF(D33="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G33" s="29" t="str">
+      <x:c r="J33" s="101" t="str">
         <x:f>IF(E33="あり",1,IF(E33="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H33" s="28"/>
-      <x:c r="I33" s="28"/>
-      <x:c r="J33" s="21"/>
-      <x:c r="K33" s="27"/>
-      <x:c r="L33" s="30" t="str">
+      <x:c r="K33" s="92"/>
+      <x:c r="L33" s="92"/>
+      <x:c r="M33" s="89"/>
+      <x:c r="N33" s="89"/>
+      <x:c r="O33" s="119" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="30" customHeight="1">
-      <x:c r="A34" s="31" t="str">
+      <x:c r="A34" s="88" t="str">
         <x:v>D27</x:v>
       </x:c>
-      <x:c r="B34" s="31" t="str">
+      <x:c r="B34" s="88" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C34" s="32"/>
-      <x:c r="D34" s="33" t="str">
+      <x:c r="C34" s="116"/>
+      <x:c r="D34" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E34" s="33" t="str">
+      <x:c r="E34" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F34" s="34" t="str">
+      <x:c r="F34" s="98"/>
+      <x:c r="G34" s="98"/>
+      <x:c r="H34" s="99" t="str">
+        <x:f>IF(D34="なし",0,IF(AND(D34="あり",ISNUMBER(F34),ISNUMBER(G34)),F34*G34,""))</x:f>
+      </x:c>
+      <x:c r="I34" s="98" t="str">
         <x:f>IF(D34="あり",1,IF(D34="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G34" s="34" t="str">
+      <x:c r="J34" s="98" t="str">
         <x:f>IF(E34="あり",1,IF(E34="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H34" s="33"/>
-      <x:c r="I34" s="33"/>
-      <x:c r="J34" s="31"/>
-      <x:c r="K34" s="35"/>
-      <x:c r="L34" s="36" t="str">
+      <x:c r="K34" s="91"/>
+      <x:c r="L34" s="91"/>
+      <x:c r="M34" s="88"/>
+      <x:c r="N34" s="88"/>
+      <x:c r="O34" s="117" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="30" customHeight="1">
-      <x:c r="A35" s="21" t="str">
+      <x:c r="A35" s="89" t="str">
         <x:v>D28</x:v>
       </x:c>
-      <x:c r="B35" s="21" t="str">
+      <x:c r="B35" s="89" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C35" s="26"/>
-      <x:c r="D35" s="28" t="str">
+      <x:c r="C35" s="118"/>
+      <x:c r="D35" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E35" s="28" t="str">
+      <x:c r="E35" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F35" s="29" t="str">
+      <x:c r="F35" s="101"/>
+      <x:c r="G35" s="101"/>
+      <x:c r="H35" s="102" t="str">
+        <x:f>IF(D35="なし",0,IF(AND(D35="あり",ISNUMBER(F35),ISNUMBER(G35)),F35*G35,""))</x:f>
+      </x:c>
+      <x:c r="I35" s="101" t="str">
         <x:f>IF(D35="あり",1,IF(D35="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G35" s="29" t="str">
+      <x:c r="J35" s="101" t="str">
         <x:f>IF(E35="あり",1,IF(E35="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H35" s="28"/>
-      <x:c r="I35" s="28"/>
-      <x:c r="J35" s="21"/>
-      <x:c r="K35" s="27"/>
-      <x:c r="L35" s="30" t="str">
+      <x:c r="K35" s="92"/>
+      <x:c r="L35" s="92"/>
+      <x:c r="M35" s="89"/>
+      <x:c r="N35" s="89"/>
+      <x:c r="O35" s="119" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="30" customHeight="1">
-      <x:c r="A36" s="31" t="str">
+      <x:c r="A36" s="88" t="str">
         <x:v>D29</x:v>
       </x:c>
-      <x:c r="B36" s="31" t="str">
+      <x:c r="B36" s="88" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C36" s="32"/>
-      <x:c r="D36" s="33" t="str">
+      <x:c r="C36" s="116"/>
+      <x:c r="D36" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E36" s="33" t="str">
+      <x:c r="E36" s="91" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F36" s="34" t="str">
+      <x:c r="F36" s="98"/>
+      <x:c r="G36" s="98"/>
+      <x:c r="H36" s="99" t="str">
+        <x:f>IF(D36="なし",0,IF(AND(D36="あり",ISNUMBER(F36),ISNUMBER(G36)),F36*G36,""))</x:f>
+      </x:c>
+      <x:c r="I36" s="98" t="str">
         <x:f>IF(D36="あり",1,IF(D36="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G36" s="34" t="str">
+      <x:c r="J36" s="98" t="str">
         <x:f>IF(E36="あり",1,IF(E36="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H36" s="33"/>
-      <x:c r="I36" s="33"/>
-      <x:c r="J36" s="31"/>
-      <x:c r="K36" s="35"/>
-      <x:c r="L36" s="36" t="str">
+      <x:c r="K36" s="91"/>
+      <x:c r="L36" s="91"/>
+      <x:c r="M36" s="88"/>
+      <x:c r="N36" s="88"/>
+      <x:c r="O36" s="117" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="30" customHeight="1">
-      <x:c r="A37" s="21" t="str">
+      <x:c r="A37" s="89" t="str">
         <x:v>D30</x:v>
       </x:c>
-      <x:c r="B37" s="21" t="str">
+      <x:c r="B37" s="89" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="C37" s="26"/>
-      <x:c r="D37" s="28" t="str">
+      <x:c r="C37" s="118"/>
+      <x:c r="D37" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="E37" s="28" t="str">
+      <x:c r="E37" s="92" t="str">
         <x:v>原票なし</x:v>
       </x:c>
-      <x:c r="F37" s="29" t="str">
+      <x:c r="F37" s="101"/>
+      <x:c r="G37" s="101"/>
+      <x:c r="H37" s="102" t="str">
+        <x:f>IF(D37="なし",0,IF(AND(D37="あり",ISNUMBER(F37),ISNUMBER(G37)),F37*G37,""))</x:f>
+      </x:c>
+      <x:c r="I37" s="101" t="str">
         <x:f>IF(D37="あり",1,IF(D37="なし",0,""))</x:f>
       </x:c>
-      <x:c r="G37" s="29" t="str">
+      <x:c r="J37" s="101" t="str">
         <x:f>IF(E37="あり",1,IF(E37="なし",0,""))</x:f>
       </x:c>
-      <x:c r="H37" s="28"/>
-      <x:c r="I37" s="28"/>
-      <x:c r="J37" s="21"/>
-      <x:c r="K37" s="27"/>
-      <x:c r="L37" s="30" t="str">
+      <x:c r="K37" s="92"/>
+      <x:c r="L37" s="92"/>
+      <x:c r="M37" s="89"/>
+      <x:c r="N37" s="89"/>
+      <x:c r="O37" s="119" t="str">
         <x:v>添付PDFに該当原票なし。未実施かどうかは不明。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="D2:D37">
-    <x:cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
-      <x:formula>"あり"</x:formula>
-    </x:cfRule>
-    <x:cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
-      <x:formula>"原票なし"</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="E2:E37">
-    <x:cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
-      <x:formula>"あり"</x:formula>
-    </x:cfRule>
-    <x:cfRule type="cellIs" dxfId="15" priority="4" operator="equal">
-      <x:formula>"原票なし"</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:dataValidations count="1">
+  <x:dataValidations count="3">
+    <x:dataValidation type="whole" operator="between" sqref="F2:F37">
+      <x:formula1>1</x:formula1>
+      <x:formula2>4</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="G2:G37">
+      <x:formula1>1</x:formula1>
+      <x:formula2>3</x:formula2>
+    </x:dataValidation>
     <x:dataValidation type="list" sqref="D2:E37">
       <x:formula1>"あり,なし,原票なし,判定不能"</x:formula1>
     </x:dataValidation>
